--- a/Assignment/api.xlsx
+++ b/Assignment/api.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" tabRatio="500" firstSheet="2"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Functional Testing" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="325">
   <si>
     <t>E-Commerce REST API — Functional Test Results</t>
   </si>
@@ -73,9 +73,6 @@
     <t>POST</t>
   </si>
   <si>
-    <t>/userreg</t>
-  </si>
-  <si>
     <t>Valid user registration — all fields correct</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
   </si>
   <si>
     <t>All mandatory fields accepted; user created in DB</t>
-  </si>
-  <si>
-    <t>/userlogin</t>
   </si>
   <si>
     <t>Valid login with correct credentials</t>
@@ -1912,31 +1906,31 @@
         <v>15</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="G5" s="5">
         <v>200</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>21</v>
-      </c>
       <c r="K5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -1950,31 +1944,31 @@
         <v>15</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G6" s="5">
         <v>200</v>
       </c>
       <c r="H6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="K6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -1982,37 +1976,37 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" s="13">
         <v>200</v>
       </c>
       <c r="H7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -2020,37 +2014,37 @@
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8" s="13">
         <v>201</v>
       </c>
       <c r="H8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -2058,37 +2052,37 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="10">
         <v>400</v>
       </c>
       <c r="H9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -2096,37 +2090,37 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>318</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>320</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="G10" s="5">
         <v>200</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -2134,37 +2128,37 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11" s="10">
         <v>404</v>
       </c>
       <c r="H11" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -2172,37 +2166,37 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G12" s="12">
         <v>400</v>
       </c>
       <c r="H12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2246,7 +2240,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B1" s="54"/>
       <c r="C1" s="54"/>
@@ -2262,7 +2256,7 @@
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -2282,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>4</v>
@@ -2291,22 +2285,22 @@
         <v>5</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>68</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>70</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>12</v>
@@ -2317,458 +2311,458 @@
     </row>
     <row r="5" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G5" s="12">
         <v>400</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="K5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G6" s="10">
         <v>429</v>
       </c>
       <c r="H6" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G7" s="12">
         <v>400</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="K7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="G8" s="10">
         <v>403</v>
       </c>
       <c r="H8" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="K8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="G9" s="12">
         <v>401</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G10" s="10">
         <v>401</v>
       </c>
       <c r="H10" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G11" s="12">
         <v>400</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G12" s="10">
         <v>400</v>
       </c>
       <c r="H12" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G13" s="5">
         <v>200</v>
       </c>
       <c r="H13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G14" s="13">
         <v>200</v>
       </c>
       <c r="H14" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="K14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G15" s="5">
         <v>200</v>
       </c>
       <c r="H15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="F16" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="G16" s="13">
         <v>200</v>
       </c>
       <c r="H16" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="L16" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="K16" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2808,7 +2802,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B1" s="54"/>
       <c r="C1" s="54"/>
@@ -2826,7 +2820,7 @@
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B2" s="57"/>
       <c r="C2" s="57"/>
@@ -2854,31 +2848,31 @@
         <v>4</v>
       </c>
       <c r="D4" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="G4" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="H4" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="I4" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="J4" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="K4" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="L4" s="21" t="s">
         <v>162</v>
-      </c>
-      <c r="K4" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>164</v>
       </c>
       <c r="M4" s="21" t="s">
         <v>12</v>
@@ -2889,16 +2883,16 @@
     </row>
     <row r="5" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>163</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>316</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E5" s="22">
         <v>10</v>
@@ -2922,27 +2916,27 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>16</v>
+        <v>167</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>316</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E6" s="24">
         <v>50</v>
@@ -2966,27 +2960,27 @@
         <v>0.4</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>170</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>316</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E7" s="22">
         <v>200</v>
@@ -3010,27 +3004,27 @@
         <v>2.1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>24</v>
+        <v>174</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>316</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E8" s="24">
         <v>10</v>
@@ -3054,27 +3048,27 @@
         <v>0</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>177</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>316</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E9" s="22">
         <v>100</v>
@@ -3098,27 +3092,27 @@
         <v>0.2</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M9" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E10" s="24">
         <v>5</v>
@@ -3142,27 +3136,27 @@
         <v>0</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E11" s="22">
         <v>10</v>
@@ -3186,27 +3180,27 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E12" s="24">
         <v>50</v>
@@ -3230,27 +3224,27 @@
         <v>0.6</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E13" s="22">
         <v>20</v>
@@ -3274,27 +3268,27 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E14" s="24">
         <v>200</v>
@@ -3318,27 +3312,27 @@
         <v>0.1</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M14" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E15" s="22">
         <v>50</v>
@@ -3362,27 +3356,27 @@
         <v>0.05</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E16" s="24">
         <v>10</v>
@@ -3406,13 +3400,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3423,6 +3417,11 @@
   <hyperlinks>
     <hyperlink ref="B10" r:id="rId1"/>
     <hyperlink ref="B16" r:id="rId2"/>
+    <hyperlink ref="B9" r:id="rId3"/>
+    <hyperlink ref="B8" r:id="rId4"/>
+    <hyperlink ref="B7" r:id="rId5"/>
+    <hyperlink ref="B6" r:id="rId6"/>
+    <hyperlink ref="B5" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3447,7 +3446,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B1" s="54"/>
       <c r="C1" s="54"/>
@@ -3463,7 +3462,7 @@
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B2" s="55"/>
       <c r="C2" s="55"/>
@@ -3489,22 +3488,22 @@
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>12</v>
@@ -3515,702 +3514,702 @@
     </row>
     <row r="5" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F5" s="29">
         <v>200</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="I5" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="J5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F6" s="32">
         <v>400</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F7" s="34">
         <v>409</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F8" s="32">
         <v>400</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F9" s="29">
         <v>200</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="I9" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="H9" s="29" t="s">
-        <v>228</v>
-      </c>
-      <c r="I9" s="31" t="s">
-        <v>210</v>
-      </c>
       <c r="J9" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F10" s="32">
         <v>401</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I10" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F11" s="34">
         <v>400</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F12" s="32">
         <v>400</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I12" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F13" s="29">
         <v>200</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="I13" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="H13" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>210</v>
-      </c>
       <c r="J13" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F14" s="32">
         <v>401</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F15" s="29">
         <v>201</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F16" s="32">
         <v>401</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I16" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F17" s="34">
         <v>401</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I17" s="31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F18" s="32">
         <v>409</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F19" s="29">
         <v>200</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="I19" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="H19" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>210</v>
-      </c>
       <c r="J19" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>317</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="52" t="s">
-        <v>319</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="F20" s="32">
         <v>401</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>318</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="49" t="s">
-        <v>320</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="F21" s="29">
         <v>200</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="I21" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="H21" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="I21" s="31" t="s">
-        <v>210</v>
-      </c>
       <c r="J21" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>271</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="52" t="s">
-        <v>320</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="F22" s="32">
         <v>404</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I22" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F23" s="34">
         <v>401</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>278</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="52" t="s">
-        <v>320</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>280</v>
       </c>
       <c r="F24" s="32">
         <v>400</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I24" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -4258,7 +4257,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B1" s="54"/>
       <c r="C1" s="54"/>
@@ -4272,7 +4271,7 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B2" s="55"/>
       <c r="C2" s="55"/>
@@ -4287,25 +4286,25 @@
     <row r="3" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="C4" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="F4" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>285</v>
-      </c>
       <c r="H4" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4322,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G5" s="36">
         <v>12</v>
@@ -4334,28 +4333,28 @@
     <row r="7" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="35" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4372,7 +4371,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G9" s="36">
         <v>20</v>
@@ -4387,25 +4386,25 @@
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="40" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C12" s="40">
         <v>61</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E12" s="41">
         <v>56</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G12" s="42">
         <v>3</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I12" s="43">
         <v>2</v>
@@ -4414,7 +4413,7 @@
     <row r="13" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="60" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
@@ -4426,30 +4425,30 @@
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="G15" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C16" s="22">
         <v>8</v>
@@ -4464,15 +4463,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="24" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C17" s="24">
         <v>12</v>
@@ -4487,15 +4486,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C18" s="22">
         <v>12</v>
@@ -4510,15 +4509,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C19" s="24">
         <v>20</v>
@@ -4533,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="2:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="61" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C22" s="61"/>
       <c r="D22" s="61"/>
@@ -4554,10 +4553,10 @@
     </row>
     <row r="23" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="44" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="59"/>
@@ -4568,10 +4567,10 @@
     </row>
     <row r="24" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="45" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D24" s="58"/>
       <c r="E24" s="58"/>
@@ -4582,10 +4581,10 @@
     </row>
     <row r="25" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="46" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D25" s="59"/>
       <c r="E25" s="59"/>
@@ -4596,10 +4595,10 @@
     </row>
     <row r="26" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="47" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D26" s="58"/>
       <c r="E26" s="58"/>
@@ -4610,10 +4609,10 @@
     </row>
     <row r="27" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="48" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D27" s="59"/>
       <c r="E27" s="59"/>
